--- a/movement.xlsx
+++ b/movement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91730\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B99142-9A3B-48F3-B9EB-3C6343E8B7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800D6E04-263C-4EE7-A30A-1DEB9D4537C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="48">
   <si>
     <t xml:space="preserve">बंद घरे </t>
   </si>
@@ -42,15 +42,6 @@
     <t xml:space="preserve">शिंगाडे वस्ती   </t>
   </si>
   <si>
-    <t xml:space="preserve">भुजबळ वस्ती </t>
-  </si>
-  <si>
-    <t xml:space="preserve">शेख वस्ती </t>
-  </si>
-  <si>
-    <t xml:space="preserve">भोंग वस्ती </t>
-  </si>
-  <si>
     <t xml:space="preserve">      सार्वजनिक       सुट्टी </t>
   </si>
   <si>
@@ -160,6 +151,24 @@
   </si>
   <si>
     <t>वस्तीचे नाव</t>
+  </si>
+  <si>
+    <t xml:space="preserve">मुक्ताईनगर  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">गावठाण   </t>
+  </si>
+  <si>
+    <t>भुजबळ वस्ती, भोंग वस्ती</t>
+  </si>
+  <si>
+    <t>तांबोळी वस्ती</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ननवरे मळा, चवरे वस्ती </t>
+  </si>
+  <si>
+    <t xml:space="preserve">गंधारे वस्ती </t>
   </si>
 </sst>
 </file>
@@ -912,22 +921,22 @@
   <dimension ref="A1:AH12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
     <col min="10" max="10" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="38" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C1" s="31" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1" s="29" t="s">
         <v>1</v>
@@ -936,96 +945,96 @@
         <v>2</v>
       </c>
       <c r="G1" s="31" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="I1" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="26" t="s">
+      <c r="N1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="O1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="P1" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="Q1" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="26" t="s">
+      <c r="R1" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="S1" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="26" t="s">
+      <c r="T1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="U1" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="26" t="s">
+      <c r="V1" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="27" t="s">
+      <c r="W1" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="28" t="s">
+      <c r="X1" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="V1" s="30" t="s">
+      <c r="Y1" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="28" t="s">
+      <c r="Z1" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="AA1" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="Y1" s="28" t="s">
+      <c r="AB1" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="Z1" s="30" t="s">
+      <c r="AC1" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="AA1" s="28" t="s">
+      <c r="AD1" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE1" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="AB1" s="30" t="s">
+      <c r="AF1" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="AC1" s="28" t="s">
+      <c r="AG1" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="AD1" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="AE1" s="28" t="s">
+      <c r="AH1" s="30" t="s">
         <v>37</v>
-      </c>
-      <c r="AF1" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG1" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="AH1" s="30" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2">
         <v>200</v>
@@ -1034,22 +1043,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="1">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="F2" s="1">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="G2" s="1">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="H2" s="3">
         <v>5</v>
       </c>
       <c r="I2" s="1">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="K2" s="5">
         <v>1</v>
@@ -1126,7 +1135,7 @@
     </row>
     <row r="3" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>3</v>
@@ -1135,25 +1144,25 @@
         <v>200</v>
       </c>
       <c r="D3" s="10">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="E3" s="10">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="F3" s="1">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="G3" s="1">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="H3" s="3">
         <v>5</v>
       </c>
       <c r="I3" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J3" s="4">
-        <v>110</v>
+        <v>211</v>
       </c>
       <c r="K3" s="7">
         <v>2</v>
@@ -1230,7 +1239,7 @@
     </row>
     <row r="4" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>3</v>
@@ -1239,25 +1248,25 @@
         <v>200</v>
       </c>
       <c r="D4" s="10">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="E4" s="10">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="F4" s="1">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="G4" s="1">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="H4" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4">
-        <v>110</v>
+        <v>218</v>
       </c>
       <c r="K4" s="5">
         <v>6</v>
@@ -1334,34 +1343,34 @@
     </row>
     <row r="5" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>43</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>4</v>
       </c>
       <c r="C5" s="2">
         <v>200</v>
       </c>
       <c r="D5" s="10">
-        <v>151</v>
+        <v>247</v>
       </c>
       <c r="E5" s="10">
-        <v>200</v>
+        <v>316</v>
       </c>
       <c r="F5" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G5" s="1">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="H5" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1">
         <v>4</v>
       </c>
       <c r="J5" s="4">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="K5" s="7">
         <v>3</v>
@@ -1438,7 +1447,7 @@
     </row>
     <row r="6" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>4</v>
@@ -1447,25 +1456,25 @@
         <v>200</v>
       </c>
       <c r="D6" s="10">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="E6" s="10">
-        <v>250</v>
+        <v>375</v>
       </c>
       <c r="F6" s="1">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G6" s="1">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H6" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J6" s="4">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="K6" s="5">
         <v>7</v>
@@ -1542,34 +1551,34 @@
     </row>
     <row r="7" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="2">
         <v>200</v>
       </c>
       <c r="D7" s="10">
-        <v>251</v>
+        <v>376</v>
       </c>
       <c r="E7" s="10">
-        <v>300</v>
+        <v>433</v>
       </c>
       <c r="F7" s="1">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G7" s="1">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H7" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J7" s="4">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="K7" s="7">
         <v>5</v>
@@ -1646,34 +1655,34 @@
     </row>
     <row r="8" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2">
         <v>200</v>
       </c>
       <c r="D8" s="10">
-        <v>301</v>
+        <v>434</v>
       </c>
       <c r="E8" s="10">
-        <v>350</v>
+        <v>509</v>
       </c>
       <c r="F8" s="1">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="G8" s="1">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="K8" s="5">
         <v>8</v>
@@ -1750,34 +1759,34 @@
     </row>
     <row r="9" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2">
         <v>200</v>
       </c>
       <c r="D9" s="10">
-        <v>351</v>
+        <v>510</v>
       </c>
       <c r="E9" s="10">
-        <v>400</v>
+        <v>572</v>
       </c>
       <c r="F9" s="1">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G9" s="1">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
         <v>5</v>
       </c>
-      <c r="I9" s="1">
-        <v>4</v>
-      </c>
       <c r="J9" s="4">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="K9" s="7">
         <v>9</v>
@@ -1854,34 +1863,34 @@
     </row>
     <row r="10" spans="1:34" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2">
         <v>200</v>
       </c>
       <c r="D10" s="10">
-        <v>451</v>
+        <v>573</v>
       </c>
       <c r="E10" s="10">
-        <v>500</v>
+        <v>627</v>
       </c>
       <c r="F10" s="1">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G10" s="1">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="K10" s="5">
         <v>12</v>
@@ -1958,34 +1967,34 @@
     </row>
     <row r="11" spans="1:34" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C11" s="19">
         <v>200</v>
       </c>
       <c r="D11" s="13">
-        <v>551</v>
+        <v>628</v>
       </c>
       <c r="E11" s="13">
-        <v>600</v>
+        <v>672</v>
       </c>
       <c r="F11" s="20">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G11" s="20">
         <v>45</v>
       </c>
       <c r="H11" s="21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I11" s="20">
         <v>4</v>
       </c>
       <c r="J11" s="22">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="K11" s="14">
         <v>13</v>
@@ -2062,7 +2071,7 @@
     </row>
     <row r="12" spans="1:34" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B12" s="36"/>
       <c r="C12" s="18"/>
@@ -2071,7 +2080,7 @@
       <c r="F12" s="39"/>
       <c r="G12" s="10"/>
       <c r="H12" s="23" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I12" s="24"/>
       <c r="J12" s="24"/>
@@ -2085,10 +2094,10 @@
       </c>
       <c r="O12" s="25"/>
       <c r="P12" s="25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q12" s="25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R12" s="25"/>
       <c r="S12" s="25">
@@ -2120,7 +2129,7 @@
         <v>20</v>
       </c>
       <c r="AE12" s="25" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AF12" s="25">
         <v>24</v>

--- a/movement.xlsx
+++ b/movement.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91730\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800D6E04-263C-4EE7-A30A-1DEB9D4537C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98991522-EAE9-44AA-B674-E91E32F3C609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1037,7 +1046,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="2">
-        <v>200</v>
+        <v>369</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -1141,7 +1150,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2">
-        <v>200</v>
+        <v>358</v>
       </c>
       <c r="D3" s="10">
         <v>83</v>
@@ -1245,7 +1254,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>200</v>
+        <v>348</v>
       </c>
       <c r="D4" s="10">
         <v>164</v>
@@ -1349,7 +1358,7 @@
         <v>43</v>
       </c>
       <c r="C5" s="2">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="D5" s="10">
         <v>247</v>
@@ -1453,7 +1462,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="2">
-        <v>200</v>
+        <v>281</v>
       </c>
       <c r="D6" s="10">
         <v>317</v>
@@ -1557,7 +1566,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="2">
-        <v>200</v>
+        <v>336</v>
       </c>
       <c r="D7" s="10">
         <v>376</v>
@@ -1661,7 +1670,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="2">
-        <v>200</v>
+        <v>443</v>
       </c>
       <c r="D8" s="10">
         <v>434</v>
@@ -1765,7 +1774,7 @@
         <v>45</v>
       </c>
       <c r="C9" s="2">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="D9" s="10">
         <v>510</v>
@@ -1869,7 +1878,7 @@
         <v>46</v>
       </c>
       <c r="C10" s="2">
-        <v>200</v>
+        <v>276</v>
       </c>
       <c r="D10" s="10">
         <v>573</v>
@@ -1973,7 +1982,7 @@
         <v>47</v>
       </c>
       <c r="C11" s="19">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="D11" s="13">
         <v>628</v>

--- a/movement.xlsx
+++ b/movement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91730\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98991522-EAE9-44AA-B674-E91E32F3C609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD58B01-82A9-4986-82B9-9E3E857E22C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1326,7 +1326,7 @@
         <v>18</v>
       </c>
       <c r="AA4" s="5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AB4" s="6">
         <v>18</v>
@@ -1409,7 +1409,7 @@
         <v>7</v>
       </c>
       <c r="T5" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U5" s="7">
         <v>5</v>
@@ -1430,7 +1430,7 @@
         <v>20</v>
       </c>
       <c r="AA5" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB5" s="6">
         <v>19</v>
@@ -1507,13 +1507,13 @@
         <v>8</v>
       </c>
       <c r="R6" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="S6" s="9">
         <v>8</v>
       </c>
       <c r="T6" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U6" s="5">
         <v>6</v>
@@ -1534,7 +1534,7 @@
         <v>21</v>
       </c>
       <c r="AA6" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB6" s="6">
         <v>21</v>
@@ -1590,73 +1590,73 @@
         <v>157</v>
       </c>
       <c r="K7" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L7" s="6">
         <v>22</v>
       </c>
       <c r="M7" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N7" s="6">
         <v>23</v>
       </c>
       <c r="O7" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P7" s="8">
         <v>23</v>
       </c>
       <c r="Q7" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R7" s="6">
         <v>22</v>
       </c>
       <c r="S7" s="11">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T7" s="6">
         <v>22</v>
       </c>
       <c r="U7" s="7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V7" s="6">
         <v>22</v>
       </c>
       <c r="W7" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X7" s="6">
         <v>22</v>
       </c>
       <c r="Y7" s="7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z7" s="6">
         <v>22</v>
       </c>
       <c r="AA7" s="7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB7" s="6">
         <v>22</v>
       </c>
       <c r="AC7" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AD7" s="6">
         <v>23</v>
       </c>
       <c r="AE7" s="7">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AF7" s="6">
         <v>23</v>
       </c>
       <c r="AG7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH7" s="6">
         <v>21</v>
@@ -1694,73 +1694,73 @@
         <v>187</v>
       </c>
       <c r="K8" s="5">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L8" s="6">
         <v>23</v>
       </c>
       <c r="M8" s="12">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="N8" s="6">
         <v>24</v>
       </c>
       <c r="O8" s="12">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P8" s="8">
         <v>24</v>
       </c>
       <c r="Q8" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R8" s="6">
         <v>23</v>
       </c>
       <c r="S8" s="9">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T8" s="6">
         <v>25</v>
       </c>
       <c r="U8" s="5">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V8" s="6">
         <v>23</v>
       </c>
       <c r="W8" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X8" s="6">
         <v>23</v>
       </c>
       <c r="Y8" s="5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Z8" s="6">
         <v>23</v>
       </c>
       <c r="AA8" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB8" s="6">
         <v>23</v>
       </c>
       <c r="AC8" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AD8" s="6">
         <v>26</v>
       </c>
       <c r="AE8" s="5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AF8" s="6">
         <v>25</v>
       </c>
       <c r="AG8" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH8" s="6">
         <v>22</v>
@@ -2134,9 +2134,7 @@
       <c r="AC12" s="25">
         <v>2</v>
       </c>
-      <c r="AD12" s="25">
-        <v>20</v>
-      </c>
+      <c r="AD12" s="25"/>
       <c r="AE12" s="25" t="s">
         <v>9</v>
       </c>
